--- a/data/cache/cloud_backup.xlsx
+++ b/data/cache/cloud_backup.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="申請列表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="草稿列表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="草稿列表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +674,21 @@
           <t>_sheet_name</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>payment_target</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>attachment_files</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>signature_file</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -684,7 +698,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -697,8 +711,16 @@
           <t>2026-03-15T16:00:00.000Z</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>115GO004/防檢署計畫</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
@@ -789,7 +811,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-03-16T07:36:57.000Z</t>
+          <t>2026-03-16T11:49:40.000Z</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -813,443 +835,26 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>EVT-2880feae-8de0-4c70-87d7-d278fa5ee780</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2026-03-16T07:36:57.000Z</t>
-        </is>
-      </c>
+          <t>d5e6b782a217415a81cbe8c9b1dfbb9c</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>申請表單</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AW3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>record_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>form_type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>form_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>plan_code</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>purpose_desc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>employee_enabled</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>employee_name</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>employee_no</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>advance_offset_enabled</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>advance_amount</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>offset_amount</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>balance_refund_amount</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>supplement_amount</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_enabled</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_name</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_address</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_payee_name</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>receipt_count</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>amount_untaxed</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>tax_mode</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>amount_total</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>handler_name</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>project_manager_name</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>department_manager_name</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>accountant_name</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>note_public</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>remarks_internal</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>owner_name</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>user_email</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>actor_role</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>source_system</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>updated_by</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>last_event_id</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>last_synced_at</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>deleted_reason</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>_row_number</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>_sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9601020260315002</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>expense</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-14T16:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>茶水費</t>
-        </is>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>李政憲</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>96010</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>600</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V2" t="n">
-        <v>30</v>
-      </c>
-      <c r="W2" t="n">
-        <v>630</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>化安處</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>李政憲</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>joli@sahtech.org</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>expense</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2026-03-16T07:39:37.000Z</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>joli@sahtech.org</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2026-03-16T07:39:37.000Z</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>joli@sahtech.org</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>EVT-ea0d2bbf-b593-43be-a517-50597ef146a5</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2026-03-16T07:39:37.000Z</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
           <t>草稿列表</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1391,11 +996,7 @@
           <t>EVT-fe637d21-daad-4f39-b6df-d8adc07d87e9</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>2026-03-16T07:38:27.000Z</t>
-        </is>
-      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
         <v>3</v>
@@ -1403,6 +1004,141 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>草稿列表</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9601020260315002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>茶水費</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>96010</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>600</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W4" t="n">
+        <v>630</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>化安處</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>joli@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2026-03-15T17:10:14</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
